--- a/www/download/COUNTRY.KOR.zdW16.xlsx
+++ b/www/download/COUNTRY.KOR.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Coreia do Sul</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>1130.36881668062</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>1290.43746284637</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1248.99143744097</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>1191.13130844873</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>1144.06788191047</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>1023.93236930785</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>954.298625400853</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.376</t>
+          <t>929.18667714911</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>1081.2330386773</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>1270.08961461552</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>1155.30004681005</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>1107.51781329698</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.539</t>
+          <t>1125.90679031407</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>1094.19484015886</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1052.20514569243</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18.208</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>18.649</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>19.309</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>19.547</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>20.066</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>20.445</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>20.842</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>21.159</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>21.373</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>21.65</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>21.925</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>22.849</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>23.81</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>24.059</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>24.449</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>10.67</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10.945</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>11.444</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>11.892</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>12.389</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>12.758</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>13.181</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>13.653</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>13.969</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>14.532</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>15.036</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>15.983</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>16.821</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>17.173</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>17.547</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>42750.118</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>43320.434</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>44448.234</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>44999.902</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>47760.951</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>46490.768</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>47124.278</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>46208.376</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>46206.822</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>48314.738</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>48435.659</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>49623.627</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>49515.417</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>51651.61</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>52079.928</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>24988.067</t>
+          <t>62576462946.8099</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25316.651</t>
+          <t>60536788907.5697</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>26057.719</t>
+          <t>62239352649.597</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27118.676</t>
+          <t>64881793324.501</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29344.074</t>
+          <t>69959637636.5039</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>28960.863</t>
+          <t>68234761060.8344</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>29634.688</t>
+          <t>73939110046.5509</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>29652.591</t>
+          <t>71846510002.1379</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>30061.072</t>
+          <t>75152282570.1225</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>32249.661</t>
+          <t>72068609227.8582</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>33042.143</t>
+          <t>74926167937.8142</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>34526.728</t>
+          <t>86182880962.3513</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>34876.022</t>
+          <t>85695211700.2678</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>36450.896</t>
+          <t>88752268867.0716</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>37024.12</t>
+          <t>89188754770.9213</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12397457558.5172</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13002887590.9366</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13808907436.5382</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>15045526680.244</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>16413579133.0527</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>16081850250.738</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>16522209708.4924</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>15836520232.9218</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>15459540916.8292</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15407934853.2945</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>15711792781.2981</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>16924723373.5361</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>17941616291.0957</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>19352589300.3644</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>19889894746.653</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2732196.66630055</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2866580.97541765</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2685394.66535547</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2531016.31051657</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2323611.41356962</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1879394.69783693</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1753105.4754284</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1517781.02184487</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1603394.38875406</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1740201.6667907</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1459094.50428476</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1418261.96638657</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1389850.40833523</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1393702.92010232</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1299377.62114307</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>196163.869266876</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>191015.760329437</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>195487.348932132</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>215944.7636625</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>245798.315587704</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>254555.491119863</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>269048.743077432</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>293841.251797522</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>320499.198619366</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>310639.319145762</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>344436.313948149</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>366299.413852554</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>354858.869243238</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>374653.298982124</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>381090.260754691</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>567652.358198403</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>541108.734425948</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>560419.305804819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>636032.432890234</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>755776.863138609</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>796175.831608334</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>911662.545591614</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>993730.614887613</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>1133692.63773326</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>993564.085897903</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1141241.11676684</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1399628.92622844</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1359442.30363114</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1399774.79265294</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>1411569.61763451</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.01557995920163</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.947002219541328</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.887022497598293</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.802441122623448</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.787792519969558</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.800841479584786</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.793627397476243</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.872418344678817</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.944499656343326</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1.0930553839345</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.1030154521469</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.04001727165519</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.943861769984945</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.883515194492019</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.861453792068475</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1130.36881668062</t>
+          <t>1161.91205582119</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1290.43746284637</t>
+          <t>1187.98019975714</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1248.99143744097</t>
+          <t>1206.64525610981</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1191.13130844873</t>
+          <t>1265.19040892634</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1144.06788191047</t>
+          <t>1324.83004813651</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1023.93236930785</t>
+          <t>1260.4955929458</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>954.298625400853</t>
+          <t>1253.46085378039</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>929.18667714911</t>
+          <t>1159.91500531941</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1081.2330386773</t>
+          <t>1106.70213350225</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1270.08961461552</t>
+          <t>1060.27583895124</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1155.30004681005</t>
+          <t>1044.97855187142</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1107.51781329698</t>
+          <t>1058.93177555736</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1125.90679031407</t>
+          <t>1066.61874395708</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>1094.19484015886</t>
+          <t>1126.90051238664</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1052.20514569243</t>
+          <t>1133.54351662696</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>15087015089.2742</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>15432528112.5485</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>17896934749.5388</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>19783337302.8635</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>23372009363.3352</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>22300648416.5244</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>23009732982.9416</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>22321025777.8045</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>20793532260.1503</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>19956307285.1507</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>21374598792.3261</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.515</t>
+          <t>24971724034.1954</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>26350018574.9455</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>28611881929.191</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>29259497664.121</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>15381378675.0336</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>15785865955.1888</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>18496924250.4026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>20516340436.058</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.441</t>
+          <t>24148763059.2313</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>23291212710.5888</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>24443780301.0646</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>23730997519.5031</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>22048628409.7416</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>21079969485.9031</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.624</t>
+          <t>22769465950.7139</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>26269501061.7367</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>27239733766.682</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>29204226626.688</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>28786411801.4047</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.761</t>
+          <t>-294363585.75942</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.696</t>
+          <t>-353337842.640277</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.924</t>
+          <t>-599989500.86375</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>-733003133.194478</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.625</t>
+          <t>-776753695.896015</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3.148</t>
+          <t>-990564294.064388</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.623</t>
+          <t>-1434047318.12297</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>-1409971741.69864</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>-1255096149.59124</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3.689</t>
+          <t>-1123662200.75236</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>-1394867158.38786</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4.906</t>
+          <t>-1297777027.54128</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>5.084</t>
+          <t>-889715191.736498</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>5.507</t>
+          <t>-592344697.496951</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6.027</t>
+          <t>473085862.716338</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.176</t>
+          <t>2341.92665406796</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2313.00008569831</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>2276.96674489947</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.403</t>
+          <t>2280.43122099761</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>2368.52125028937</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.946</t>
+          <t>2269.95274861062</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2.234</t>
+          <t>2248.24172900447</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.516</t>
+          <t>2171.84613422829</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.456</t>
+          <t>2151.98191826955</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.145</t>
+          <t>2219.21605317256</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>2197.60604174768</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>3.041</t>
+          <t>2160.23911164151</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>3.084</t>
+          <t>2073.35939952753</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>3.202</t>
+          <t>2122.53423776108</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3.404</t>
+          <t>2110.03887749989</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.504</t>
+          <t>2347.91268957749</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>2322.99679246469</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.544</t>
+          <t>2301.99668261584</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>2302.1565466587</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>2380.17940194817</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>2273.93046538126</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>2261.0774969201</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>2183.88473144669</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>2161.92344037514</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>2231.60000354074</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>2209.12747403115</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1.092</t>
+          <t>2171.7794646167</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>2079.63074758209</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>2146.87679767535</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>2130.14553929991</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>191712.518295937</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>170359.586118598</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>181194.986411071</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>213912.935888814</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>280094.706141764</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>311748.591494899</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>350663.716038866</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>408211.038906533</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>486259.424988806</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>415349.564188375</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>518902.395212791</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>652058.200675404</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>670707.61857045</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>686567.764442345</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>697935.060988694</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>11354189187.4586</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>11094673145.846</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>10541434182.3732</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>11388826147.5719</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>13387533630.9686</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>12162148903.171</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>12949734926.7408</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>12793995492.2508</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>16517608687.9932</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>15557854288.5545</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>16261683725.5166</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>21088575533.0936</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>21185523524.379</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>20990023521.2324</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>20200188304.1562</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>162975.541944307</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>146130.98449251</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>155601.950265472</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>182566.196663079</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>228602.670330894</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>266562.828566227</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>316103.764888645</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>363678.337428345</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>442114.221498904</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>336425.519775869</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>440528.278738112</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>578382.132743589</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>576368.739957468</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>562223.516127372</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>562688.111082863</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>42750.118</t>
+          <t>22511282243.4741</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>43320.434</t>
+          <t>23078723194.0102</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>44448.234</t>
+          <t>24772715794.8504</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>44999.902</t>
+          <t>26940047497.5787</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>47760.951</t>
+          <t>30424795123.4761</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>46490.768</t>
+          <t>29421007474.0245</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>47124.278</t>
+          <t>32459794524.2539</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>46208.376</t>
+          <t>31248182750.7248</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>46206.822</t>
+          <t>33964546017.4814</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>48314.738</t>
+          <t>28793644155.5921</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>48435.659</t>
+          <t>31687098970.0912</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>49623.627</t>
+          <t>40765880257.2229</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>49515.417</t>
+          <t>40711115581.8768</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>51651.61</t>
+          <t>40517220696.5393</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>52079.928</t>
+          <t>39673342540.2346</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24988.067</t>
+          <t>28736.9763516301</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>25316.651</t>
+          <t>24228.6016260873</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26057.719</t>
+          <t>25593.0361455995</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27118.676</t>
+          <t>31346.7392257348</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>29344.074</t>
+          <t>51492.0358108698</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>28960.863</t>
+          <t>45185.7629286725</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>29634.688</t>
+          <t>34559.9511502209</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>29652.591</t>
+          <t>44532.7014781876</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>30061.072</t>
+          <t>44145.203489902</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>32249.661</t>
+          <t>78924.0444125062</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>33042.143</t>
+          <t>78374.1164746791</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>34526.728</t>
+          <t>73676.0679318148</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>34876.022</t>
+          <t>94338.8786129822</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>36450.896</t>
+          <t>124344.248314973</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>37024.12</t>
+          <t>135246.949905831</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>74286.722</t>
+          <t>-11157093056.0155</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>71976.085</t>
+          <t>-11984050048.1642</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>74334.171</t>
+          <t>-14231281612.4772</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>77529.433</t>
+          <t>-15551221350.0068</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>84144.958</t>
+          <t>-17037261492.5075</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>83662.509</t>
+          <t>-17258858570.8536</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>89863.821</t>
+          <t>-19510059597.5131</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>86749.974</t>
+          <t>-18454187258.474</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>90924.344</t>
+          <t>-17446937329.4882</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>87386.635</t>
+          <t>-13235789867.0376</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>90763.059</t>
+          <t>-15425415244.5746</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>105945.19</t>
+          <t>-19677304724.1293</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>105853.328</t>
+          <t>-19525592057.4978</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>109006.422</t>
+          <t>-19527197175.3069</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>89188.755</t>
+          <t>-19473154236.0784</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>265703.348558887</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>247597.97380924</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>277211.518636946</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>312825.536999076</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>365532.028609229</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>423882.585818532</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>473310.976140042</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.082</t>
+          <t>526494.436751013</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.231</t>
+          <t>472433.391294846</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>425418.513447351</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1.239</t>
+          <t>523294.12040026</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1.536</t>
+          <t>575155.705238108</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>582173.549950983</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1.538</t>
+          <t>628206.921591187</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1.412</t>
+          <t>679705.824248373</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>21624.575</t>
+          <t>0.100814486595837</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>21369.976</t>
+          <t>0.0944631119192659</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>21710.541</t>
+          <t>0.0983556696656104</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>22028.568</t>
+          <t>0.0927110554947858</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>22752.696</t>
+          <t>0.095308366912783</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>21816.202</t>
+          <t>0.0911300093366664</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>21820.82</t>
+          <t>0.0885126335841123</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>21244.659</t>
+          <t>0.0898072172439986</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>21245.835</t>
+          <t>0.0808715358787572</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>22532.36</t>
+          <t>0.079648445259255</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>22613.357</t>
+          <t>0.0876976757082449</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>22555.077</t>
+          <t>0.0838951650223387</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>22369.251</t>
+          <t>0.0805808238918371</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>23754.771</t>
+          <t>0.0789888184405501</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>24078.845</t>
+          <t>0.07722078895714</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>212118.666420918</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>205125.88877233</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>232751.241204588</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>266242.591065472</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>299826.277731002</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>362045.614367676</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>415315.144594727</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>464960.373702264</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>430496.105215812</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>386653.211644653</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>464398.117486416</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>514693.705441813</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>533112.197938188</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>575010.397123815</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.381</t>
+          <t>630270.27255921</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>14056.78</t>
+          <t>326946.51755515</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>14693.85</t>
+          <t>316783.749722492</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15642.221</t>
+          <t>354580.227185362</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>17031.544</t>
+          <t>399970.242963151</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>18617.998</t>
+          <t>440511.026762419</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>18464.343</t>
+          <t>523759.478420637</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18973.815</t>
+          <t>592150.758224056</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>18067.891</t>
+          <t>649922.72188089</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>17720.439</t>
+          <t>597086.470471031</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17649.456</t>
+          <t>528639.662754186</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>17896.431</t>
+          <t>623546.383751446</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>19493.293</t>
+          <t>680937.56094195</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>20632.27</t>
+          <t>701801.659077351</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>22159.576</t>
+          <t>756050.251712294</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>19889.895</t>
+          <t>821661.974383707</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>1760763.02574163</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>72.29</t>
+          <t>1696279.87140151</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>66.59</t>
+          <t>1923951.98913888</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>59.23</t>
+          <t>2254483.10084743</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>57.61</t>
+          <t>2625495.85987795</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>56.85</t>
+          <t>3148067.45678187</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>56.19</t>
+          <t>3623140.12525721</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>4050112.62600163</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>69.64</t>
+          <t>4010334.68967057</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>3688646.56784979</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>84.63</t>
+          <t>4192191.68889788</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>77.12</t>
+          <t>4905598.55377011</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>69.04</t>
+          <t>5084424.89302055</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>64.49</t>
+          <t>5507076.66993928</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>86.15</t>
+          <t>6027281.27876362</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.243</t>
+          <t>456016.944894788</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>481933.847961148</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.213</t>
+          <t>503585.05475812</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>3.025</t>
+          <t>517626.687105383</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.792</t>
+          <t>524803.395286095</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.301</t>
+          <t>551469.799379039</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>574851.43949295</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.838</t>
+          <t>588490.531018038</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.938</t>
+          <t>607129.605473988</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2.115</t>
+          <t>611602.466914241</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.765</t>
+          <t>637299.217900031</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.747</t>
+          <t>655665.744427275</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.719</t>
+          <t>666749.88484098</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.715</t>
+          <t>693084.451031014</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>719289.821059366</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>303978.413632416</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>318079.816968689</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>336221.704617538</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>350735.982774144</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>361218.518575042</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>384315.530532067</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>407003.850628479</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>423379.286750981</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>439069.125676553</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>447484.971001995</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>474640.804401456</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>494753.832722128</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>504012.092545297</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>522989.787124982</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>547706.023252732</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>177510.420457076</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>160235.875338599</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>189231.586296237</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>209015.507874723</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>250231.72274124</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>286883.416728987</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>320693.674330786</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>363729.34446599</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>324321.925741518</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>293794.964240123</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>367645.467239766</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>411556.000201889</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>409707.146895762</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>434997.479220023</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>465431.415612726</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>24988067000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>25316651000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>26057719000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>27118676000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>29344074000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>28960863000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>29634688000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>29652591000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>30061072000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>32249661000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>33042143000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>34526728000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>34876022000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>36450896000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>37024120000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>42750118052.9724</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>43320433560.2392</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>44448234160.0989</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>44999901787.586</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>47760951219.9437</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>46490767592.7929</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>47124278307.1451</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>46208375887.9648</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>46206822119.9894</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>48314738145.4579</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>48435658895.2367</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>49623627490.1896</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>49515417484.7972</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>51651610118.9387</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>52079928290.3435</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>21624575181.2611</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>21369976171.8863</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>21710540523.3118</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>22028567728.521</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>22752695840.3661</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>21816202431.314</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>21820820344.6363</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>21244659387.5937</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>21245834661.4116</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>22532360036.0333</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>22613357268.3337</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>22555077413.0551</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>22369250862.8657</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>23754771480.187</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>24078844845.7787</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>18207712</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>18648512</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>19308557</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>19546847</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>20066114</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>20445114</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>20841514</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>21158798</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>21373015</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>21650268</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>21925244</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>22849294</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>23809716</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>24058954</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>24449000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>10669876</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10945374</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>11444049</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>11891907</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>12389196</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>12758355</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>13181273</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>13653173</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>13969017</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>14532006</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>15035517</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>15982827</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>16821021</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>17173290</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>17546653</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>42750118052.9724</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>43320433560.2392</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>44448234160.0989</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>44999901787.586</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>47760951219.9437</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>46490767592.7929</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>47124278307.1451</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>46208375887.9648</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>46206822119.9894</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>48314738145.4579</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>48435658895.2367</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>49623627490.1896</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>49515417484.7972</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>51651610118.9387</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>52079928290.3435</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>24988067000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25316651000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>26057719000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>27118676000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>29344074000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>28960863000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>29634688000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>29652591000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>30061072000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>32249661000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>33042143000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>34526728000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>34876022000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>36450896000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>37024120000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1175975.8116288</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1100066.474877</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1248189.0194004</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1402883.109684</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1629694.6278162</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1945950.5879686</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2233897.770184</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2516486.668439</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2456129.258247</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2144878.2888442</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2638334.07438</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3040670.68324</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3083803.3577923</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3201879.2379372</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3403854.39562871</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>504456.9399408</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>477019.626084</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>543811.8137298</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>608985.753516</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>690742.7473884</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>810642.8932745</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>912844.433718</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1013652.06512</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>921408.396564</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>822434.6256322</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>991191.851424</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1092493.561812</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1111508.8081669</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1191047.7277062</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1287093.3852255</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2482781.16980935</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2630029.44622143</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2816603.51063748</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3013505.25024527</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3200253.55056237</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3386475.9969549</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3574196.3403954</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3752959.79835184</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>4007388.05456562</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4239141.46657957</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>4284653.96918647</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>4676175.31273807</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>4854201.64375942</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>5055192.46285784</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>5286375.33814187</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
